--- a/excel-files/CALOOCAN/CIELITO ZAMORA MEMORIAL SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/CIELITO ZAMORA MEMORIAL SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C5E3936-9FC7-4D78-8498-6E16FBFB8D58}"/>
+  <xr:revisionPtr revIDLastSave="537" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56DDB905-80A1-479D-8137-954ECBE9B02D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -5614,8 +5614,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -14448,8 +14448,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 X112:X127 F103:F110 R103:R110 L103:L110 X103:X110 F14:F21" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 G23:G31 G33:G41 G14:G21 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14678,7 +14678,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W3" s="5"/>
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
@@ -14755,7 +14757,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W4" s="5"/>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
@@ -14832,7 +14836,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -14909,7 +14915,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -14986,7 +14994,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -15063,7 +15073,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -15140,7 +15152,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -15217,7 +15231,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>3192</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -15295,7 +15311,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4136</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -15372,7 +15390,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4136</v>
       </c>
-      <c r="W13" s="5"/>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
@@ -15449,7 +15469,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4136</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -15526,7 +15548,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4136</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -15852,7 +15876,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4136</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -15930,7 +15956,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4176</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -16007,7 +16035,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4176</v>
       </c>
-      <c r="W22" s="5"/>
+      <c r="W22" s="5">
+        <v>0</v>
+      </c>
       <c r="X22" s="1"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5">
@@ -16084,7 +16114,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4176</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -16161,7 +16193,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4176</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -16238,7 +16272,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4176</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -16564,7 +16600,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4176</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5">
+        <v>0</v>
+      </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -16642,7 +16680,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
@@ -16719,7 +16759,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W32" s="5"/>
+      <c r="W32" s="5">
+        <v>0</v>
+      </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="5"/>
       <c r="Z32" s="5">
@@ -16796,7 +16838,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="5">
+        <v>0</v>
+      </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
@@ -16873,7 +16917,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="5">
+        <v>0</v>
+      </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
@@ -16950,7 +16996,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="5">
+        <v>0</v>
+      </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
@@ -17027,7 +17075,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="5">
+        <v>0</v>
+      </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
@@ -17104,7 +17154,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="5">
+        <v>0</v>
+      </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
@@ -17181,7 +17233,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="5">
+        <v>0</v>
+      </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
@@ -17258,7 +17312,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="5">
+        <v>0</v>
+      </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
@@ -17335,7 +17391,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="5">
+        <v>0</v>
+      </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
@@ -17412,7 +17470,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>5064</v>
       </c>
-      <c r="W41" s="5"/>
+      <c r="W41" s="5">
+        <v>0</v>
+      </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
@@ -17490,7 +17550,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="5">
+        <v>0</v>
+      </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
@@ -17567,7 +17629,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W44" s="5"/>
+      <c r="W44" s="5">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
@@ -17644,7 +17708,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="5">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
@@ -17721,7 +17787,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="5">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
@@ -17798,7 +17866,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="5">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
@@ -17875,7 +17945,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="5">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
@@ -17952,7 +18024,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="5">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
@@ -18029,7 +18103,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="5">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
@@ -18106,7 +18182,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="5">
+        <v>0</v>
+      </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
@@ -18183,7 +18261,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W52" s="5"/>
+      <c r="W52" s="5">
+        <v>0</v>
+      </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5">
@@ -18260,7 +18340,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4464</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="5">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
@@ -18350,12 +18432,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W55" s="5"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="5"/>
+      <c r="W55" s="5">
+        <v>700</v>
+      </c>
+      <c r="X55" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y55" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z55" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3396</v>
       </c>
       <c r="AA55" s="5">
         <f t="shared" si="7"/>
@@ -18439,12 +18527,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W56" s="5"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="5"/>
+      <c r="W56" s="5">
+        <v>500</v>
+      </c>
+      <c r="X56" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y56" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z56" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3596</v>
       </c>
       <c r="AA56" s="5">
         <f t="shared" si="7"/>
@@ -18528,12 +18622,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W57" s="5"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="5"/>
+      <c r="W57" s="5">
+        <v>900</v>
+      </c>
+      <c r="X57" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y57" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z57" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3196</v>
       </c>
       <c r="AA57" s="5">
         <f t="shared" si="7"/>
@@ -18571,7 +18671,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
@@ -18586,7 +18688,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="Q58" s="5"/>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
@@ -18601,9 +18705,15 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W58" s="5"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="5"/>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y58" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z58" s="5">
         <f t="shared" si="6"/>
         <v>4096</v>
@@ -18644,7 +18754,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K59" s="5"/>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
@@ -18680,12 +18792,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W59" s="5"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="5"/>
+      <c r="W59" s="5">
+        <v>600</v>
+      </c>
+      <c r="X59" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y59" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z59" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3496</v>
       </c>
       <c r="AA59" s="5">
         <f t="shared" si="7"/>
@@ -18723,7 +18841,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
@@ -18759,12 +18879,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W60" s="5"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="5"/>
+      <c r="W60" s="5">
+        <v>700</v>
+      </c>
+      <c r="X60" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y60" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z60" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3396</v>
       </c>
       <c r="AA60" s="5">
         <f t="shared" si="7"/>
@@ -18802,7 +18928,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K61" s="5"/>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
@@ -18838,12 +18966,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W61" s="5"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="5"/>
+      <c r="W61" s="5">
+        <v>300</v>
+      </c>
+      <c r="X61" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y61" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z61" s="5">
         <f>IF((V61-W61)&lt;0,0,(V61-W61))</f>
-        <v>4096</v>
+        <v>3796</v>
       </c>
       <c r="AA61" s="5">
         <f>IF((W61-V61)&lt;0,0,(W61-V61))</f>
@@ -18881,7 +19015,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K62" s="5"/>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5">
@@ -18917,12 +19053,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W62" s="5"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="5"/>
+      <c r="W62" s="5">
+        <v>900</v>
+      </c>
+      <c r="X62" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y62" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z62" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3196</v>
       </c>
       <c r="AA62" s="5">
         <f t="shared" si="7"/>
@@ -18960,7 +19102,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K63" s="5"/>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
       <c r="L63" s="1"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5">
@@ -18996,12 +19140,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W63" s="5"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="5"/>
+      <c r="W63" s="5">
+        <v>200</v>
+      </c>
+      <c r="X63" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y63" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z63" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3896</v>
       </c>
       <c r="AA63" s="5">
         <f t="shared" si="7"/>
@@ -19039,7 +19189,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K64" s="5"/>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
       <c r="L64" s="1"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5">
@@ -19075,12 +19227,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W64" s="5"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="5"/>
+      <c r="W64" s="5">
+        <v>300</v>
+      </c>
+      <c r="X64" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y64" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z64" s="5">
         <f>IF((V64-W64)&lt;0,0,(V64-W64))</f>
-        <v>4096</v>
+        <v>3796</v>
       </c>
       <c r="AA64" s="5">
         <f>IF((W64-V64)&lt;0,0,(W64-V64))</f>
@@ -19118,7 +19276,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="K65" s="5"/>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
       <c r="L65" s="1"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5">
@@ -19154,12 +19314,18 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>4096</v>
       </c>
-      <c r="W65" s="5"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="5"/>
+      <c r="W65" s="5">
+        <v>900</v>
+      </c>
+      <c r="X65" s="1">
+        <v>2025</v>
+      </c>
+      <c r="Y65" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="Z65" s="5">
         <f t="shared" si="6"/>
-        <v>4096</v>
+        <v>3196</v>
       </c>
       <c r="AA65" s="5">
         <f t="shared" si="7"/>
@@ -23453,8 +23619,8 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R2 V2:X10 T3:U10 T12:X19 Z3:AA10 Z12:AA19 T21:X29 Z21:AA29 T31:X41 Z31:AA41 T43:X53 Z43:AA53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 N3:R10 N12:R19 N21:R29 N31:R41 N43:R53" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
+    <protectedRange sqref="J2:L2 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R2 T3:U10 T12:X19 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 N3:R10 N12:R19 N21:R29 N31:R41 N43:R53 V2:X10 T21:X29 T31:X41 T43:X53 H55:L65 T55:X65" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122 Y55:Y65" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -23464,11 +23630,11 @@
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 M115:M122 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X103:X113 X67:X77 X79:X89 X91:X101 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
